--- a/testing_electricity_202604.xlsx
+++ b/testing_electricity_202604.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiffanychen/Desktop/intern/hkust_net_zero_office/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiffanychen/Desktop/intern/hkust_net_zero_office/sustainability-data-automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21AE6BDE-DDE8-3949-97EF-47327DD5E955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC729AD-CFE8-1C4F-A436-FC6C2F11B628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="780" windowWidth="21420" windowHeight="15280" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7315,16 +7315,16 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -59026,7 +59026,7 @@
       </c>
     </row>
     <row r="47" spans="1:178">
-      <c r="A47" s="278"/>
+      <c r="A47" s="275"/>
       <c r="B47" s="265">
         <v>460823</v>
       </c>
@@ -59072,40 +59072,40 @@
       <c r="P47" s="274">
         <v>10325</v>
       </c>
-      <c r="Q47" s="275">
+      <c r="Q47" s="277">
         <v>12420</v>
       </c>
-      <c r="R47" s="275">
+      <c r="R47" s="277">
         <v>12770</v>
       </c>
-      <c r="S47" s="275">
+      <c r="S47" s="277">
         <v>17157</v>
       </c>
-      <c r="T47" s="275">
+      <c r="T47" s="277">
         <v>20679</v>
       </c>
-      <c r="U47" s="275">
+      <c r="U47" s="277">
         <v>21661</v>
       </c>
-      <c r="V47" s="275">
+      <c r="V47" s="277">
         <v>19687</v>
       </c>
-      <c r="W47" s="275">
+      <c r="W47" s="277">
         <v>19598</v>
       </c>
-      <c r="X47" s="275">
+      <c r="X47" s="277">
         <v>19579</v>
       </c>
-      <c r="Y47" s="275">
+      <c r="Y47" s="277">
         <v>23913</v>
       </c>
-      <c r="Z47" s="275">
+      <c r="Z47" s="277">
         <v>22106</v>
       </c>
-      <c r="AA47" s="275">
+      <c r="AA47" s="277">
         <v>20839</v>
       </c>
-      <c r="AB47" s="275">
+      <c r="AB47" s="277">
         <v>20632</v>
       </c>
       <c r="AC47" s="274">
@@ -59177,7 +59177,7 @@
       <c r="AY47" s="274">
         <v>19565</v>
       </c>
-      <c r="AZ47" s="277">
+      <c r="AZ47" s="278">
         <v>19146</v>
       </c>
       <c r="BA47" s="276">
@@ -59569,7 +59569,7 @@
       </c>
     </row>
     <row r="48" spans="1:178" customFormat="1" ht="17">
-      <c r="A48" s="278"/>
+      <c r="A48" s="275"/>
       <c r="B48" s="265">
         <v>205337</v>
       </c>
@@ -59591,18 +59591,18 @@
       <c r="N48" s="274"/>
       <c r="O48" s="274"/>
       <c r="P48" s="274"/>
-      <c r="Q48" s="275"/>
-      <c r="R48" s="275"/>
-      <c r="S48" s="275"/>
-      <c r="T48" s="275"/>
-      <c r="U48" s="275"/>
-      <c r="V48" s="275"/>
-      <c r="W48" s="275"/>
-      <c r="X48" s="275"/>
-      <c r="Y48" s="275"/>
-      <c r="Z48" s="275"/>
-      <c r="AA48" s="275"/>
-      <c r="AB48" s="275"/>
+      <c r="Q48" s="277"/>
+      <c r="R48" s="277"/>
+      <c r="S48" s="277"/>
+      <c r="T48" s="277"/>
+      <c r="U48" s="277"/>
+      <c r="V48" s="277"/>
+      <c r="W48" s="277"/>
+      <c r="X48" s="277"/>
+      <c r="Y48" s="277"/>
+      <c r="Z48" s="277"/>
+      <c r="AA48" s="277"/>
+      <c r="AB48" s="277"/>
       <c r="AC48" s="274"/>
       <c r="AD48" s="274"/>
       <c r="AE48" s="274"/>
@@ -59626,7 +59626,7 @@
       <c r="AW48" s="274"/>
       <c r="AX48" s="274"/>
       <c r="AY48" s="274"/>
-      <c r="AZ48" s="277"/>
+      <c r="AZ48" s="278"/>
       <c r="BA48" s="276"/>
       <c r="BB48" s="276"/>
       <c r="BC48" s="276"/>
@@ -59994,7 +59994,7 @@
       </c>
     </row>
     <row r="49" spans="1:178" customFormat="1" ht="34">
-      <c r="A49" s="278"/>
+      <c r="A49" s="275"/>
       <c r="B49" s="265">
         <v>229155</v>
       </c>
@@ -67781,6 +67781,50 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="BJ47:BJ48"/>
+    <mergeCell ref="BD47:BD48"/>
+    <mergeCell ref="BE47:BE48"/>
+    <mergeCell ref="BF47:BF48"/>
+    <mergeCell ref="BG47:BG48"/>
+    <mergeCell ref="BH47:BH48"/>
+    <mergeCell ref="BI47:BI48"/>
+    <mergeCell ref="AP47:AP48"/>
+    <mergeCell ref="BC47:BC48"/>
+    <mergeCell ref="AR47:AR48"/>
+    <mergeCell ref="AS47:AS48"/>
+    <mergeCell ref="AT47:AT48"/>
+    <mergeCell ref="AU47:AU48"/>
+    <mergeCell ref="AV47:AV48"/>
+    <mergeCell ref="AW47:AW48"/>
+    <mergeCell ref="AX47:AX48"/>
+    <mergeCell ref="AY47:AY48"/>
+    <mergeCell ref="AZ47:AZ48"/>
+    <mergeCell ref="BA47:BA48"/>
+    <mergeCell ref="BB47:BB48"/>
+    <mergeCell ref="AK47:AK48"/>
+    <mergeCell ref="AL47:AL48"/>
+    <mergeCell ref="AM47:AM48"/>
+    <mergeCell ref="AN47:AN48"/>
+    <mergeCell ref="AO47:AO48"/>
+    <mergeCell ref="AF47:AF48"/>
+    <mergeCell ref="AG47:AG48"/>
+    <mergeCell ref="AH47:AH48"/>
+    <mergeCell ref="AI47:AI48"/>
+    <mergeCell ref="AJ47:AJ48"/>
     <mergeCell ref="AE47:AE48"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="BK47:BK48"/>
@@ -67797,50 +67841,6 @@
     <mergeCell ref="AC47:AC48"/>
     <mergeCell ref="AD47:AD48"/>
     <mergeCell ref="AQ47:AQ48"/>
-    <mergeCell ref="AF47:AF48"/>
-    <mergeCell ref="AG47:AG48"/>
-    <mergeCell ref="AH47:AH48"/>
-    <mergeCell ref="AI47:AI48"/>
-    <mergeCell ref="AJ47:AJ48"/>
-    <mergeCell ref="AK47:AK48"/>
-    <mergeCell ref="AL47:AL48"/>
-    <mergeCell ref="AM47:AM48"/>
-    <mergeCell ref="AN47:AN48"/>
-    <mergeCell ref="AO47:AO48"/>
-    <mergeCell ref="AP47:AP48"/>
-    <mergeCell ref="BC47:BC48"/>
-    <mergeCell ref="AR47:AR48"/>
-    <mergeCell ref="AS47:AS48"/>
-    <mergeCell ref="AT47:AT48"/>
-    <mergeCell ref="AU47:AU48"/>
-    <mergeCell ref="AV47:AV48"/>
-    <mergeCell ref="AW47:AW48"/>
-    <mergeCell ref="AX47:AX48"/>
-    <mergeCell ref="AY47:AY48"/>
-    <mergeCell ref="AZ47:AZ48"/>
-    <mergeCell ref="BA47:BA48"/>
-    <mergeCell ref="BB47:BB48"/>
-    <mergeCell ref="BJ47:BJ48"/>
-    <mergeCell ref="BD47:BD48"/>
-    <mergeCell ref="BE47:BE48"/>
-    <mergeCell ref="BF47:BF48"/>
-    <mergeCell ref="BG47:BG48"/>
-    <mergeCell ref="BH47:BH48"/>
-    <mergeCell ref="BI47:BI48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:P48"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -67854,6 +67854,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Loretta xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
@@ -67866,15 +67875,6 @@
     <TaxCatchAll xmlns="be3055c3-5ee9-432b-9d2b-e9bb13d3524a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -68153,20 +68153,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4277783-1FC0-4518-9AC7-78441643C7FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{771927D8-23AB-4166-821E-2FB8CF69E88F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="bc76fe4c-a155-4cd4-b3ce-e749a30fe160"/>
     <ds:schemaRef ds:uri="be3055c3-5ee9-432b-9d2b-e9bb13d3524a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4277783-1FC0-4518-9AC7-78441643C7FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/testing_electricity_202604.xlsx
+++ b/testing_electricity_202604.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiffanychen/Desktop/intern/hkust_net_zero_office/sustainability-data-automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC729AD-CFE8-1C4F-A436-FC6C2F11B628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978A3109-FBD2-454A-81D2-CB9DD54988C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="780" windowWidth="21420" windowHeight="15280" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="780" windowWidth="26160" windowHeight="16780" tabRatio="887" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CLP Tariff" sheetId="2" r:id="rId1"/>
@@ -3829,7 +3829,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="254">
   <si>
     <t>Total 
 (Group A) (kWh)</t>
@@ -4756,6 +4756,9 @@
   </si>
   <si>
     <t>RB2</t>
+  </si>
+  <si>
+    <t>HELLOOOO</t>
   </si>
 </sst>
 </file>
@@ -20502,17 +20505,17 @@
     <col min="43" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="29">
+    <row r="1" spans="1:36" ht="29">
       <c r="A1" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:36" ht="18.5" customHeight="1" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="65" thickBot="1">
+    <row r="3" spans="1:36" ht="65" thickBot="1">
       <c r="A3" s="222" t="s">
         <v>45</v>
       </c>
@@ -20615,8 +20618,11 @@
       <c r="AI3" s="251" t="s">
         <v>76</v>
       </c>
+      <c r="AJ3" s="4" t="s">
+        <v>253</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" ht="26" customHeight="1">
+    <row r="4" spans="1:36" ht="26" customHeight="1">
       <c r="A4" s="35">
         <v>41640</v>
       </c>
@@ -20716,7 +20722,7 @@
       <c r="AH4" s="36"/>
       <c r="AI4" s="36"/>
     </row>
-    <row r="5" spans="1:35" ht="23" customHeight="1">
+    <row r="5" spans="1:36" ht="23" customHeight="1">
       <c r="A5" s="35">
         <v>41671</v>
       </c>
@@ -20816,7 +20822,7 @@
       <c r="AH5" s="37"/>
       <c r="AI5" s="37"/>
     </row>
-    <row r="6" spans="1:35" ht="23" customHeight="1">
+    <row r="6" spans="1:36" ht="23" customHeight="1">
       <c r="A6" s="35">
         <v>41699</v>
       </c>
@@ -20916,7 +20922,7 @@
       <c r="AH6" s="37"/>
       <c r="AI6" s="37"/>
     </row>
-    <row r="7" spans="1:35" ht="22.25" customHeight="1">
+    <row r="7" spans="1:36" ht="22.25" customHeight="1">
       <c r="A7" s="35">
         <v>41730</v>
       </c>
@@ -21016,7 +21022,7 @@
       <c r="AH7" s="37"/>
       <c r="AI7" s="37"/>
     </row>
-    <row r="8" spans="1:35" ht="23.5" customHeight="1">
+    <row r="8" spans="1:36" ht="23.5" customHeight="1">
       <c r="A8" s="35">
         <v>41760</v>
       </c>
@@ -21116,7 +21122,7 @@
       <c r="AH8" s="37"/>
       <c r="AI8" s="37"/>
     </row>
-    <row r="9" spans="1:35" ht="25.25" customHeight="1">
+    <row r="9" spans="1:36" ht="25.25" customHeight="1">
       <c r="A9" s="35">
         <v>41791</v>
       </c>
@@ -21216,7 +21222,7 @@
       <c r="AH9" s="37"/>
       <c r="AI9" s="37"/>
     </row>
-    <row r="10" spans="1:35" ht="23.25" customHeight="1">
+    <row r="10" spans="1:36" ht="23.25" customHeight="1">
       <c r="A10" s="35">
         <v>41821</v>
       </c>
@@ -21316,7 +21322,7 @@
       <c r="AH10" s="36"/>
       <c r="AI10" s="36"/>
     </row>
-    <row r="11" spans="1:35" ht="23.25" customHeight="1">
+    <row r="11" spans="1:36" ht="23.25" customHeight="1">
       <c r="A11" s="39">
         <v>41852</v>
       </c>
@@ -21416,7 +21422,7 @@
       <c r="AH11" s="40"/>
       <c r="AI11" s="40"/>
     </row>
-    <row r="12" spans="1:35" ht="23.25" customHeight="1">
+    <row r="12" spans="1:36" ht="23.25" customHeight="1">
       <c r="A12" s="39">
         <v>41883</v>
       </c>
@@ -21516,7 +21522,7 @@
       <c r="AH12" s="40"/>
       <c r="AI12" s="40"/>
     </row>
-    <row r="13" spans="1:35" ht="23.25" customHeight="1">
+    <row r="13" spans="1:36" ht="23.25" customHeight="1">
       <c r="A13" s="39">
         <v>41913</v>
       </c>
@@ -21616,7 +21622,7 @@
       <c r="AH13" s="40"/>
       <c r="AI13" s="40"/>
     </row>
-    <row r="14" spans="1:35" ht="23.25" customHeight="1">
+    <row r="14" spans="1:36" ht="23.25" customHeight="1">
       <c r="A14" s="39">
         <v>41944</v>
       </c>
@@ -21716,7 +21722,7 @@
       <c r="AH14" s="40"/>
       <c r="AI14" s="40"/>
     </row>
-    <row r="15" spans="1:35" ht="23.25" customHeight="1">
+    <row r="15" spans="1:36" ht="23.25" customHeight="1">
       <c r="A15" s="39">
         <v>41974</v>
       </c>
@@ -21816,7 +21822,7 @@
       <c r="AH15" s="40"/>
       <c r="AI15" s="40"/>
     </row>
-    <row r="16" spans="1:35" ht="23.25" customHeight="1">
+    <row r="16" spans="1:36" ht="23.25" customHeight="1">
       <c r="A16" s="44">
         <v>42005</v>
       </c>
@@ -35443,6 +35449,9 @@
       </c>
       <c r="AI149" s="168">
         <v>43012</v>
+      </c>
+      <c r="AJ149" s="4">
+        <v>10000000</v>
       </c>
     </row>
     <row r="150" spans="1:41" ht="23.25" customHeight="1">
@@ -67854,30 +67863,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Loretta xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Skiee xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
-    <Marcusshortlist xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
-    <Notes xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
-    <TaxCatchAll xmlns="be3055c3-5ee9-432b-9d2b-e9bb13d3524a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A29A70560454A24D9B372805159B7667" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14f976c721eda7b2b215a20b4d5a78d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xmlns:ns3="be3055c3-5ee9-432b-9d2b-e9bb13d3524a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="403c36ed6babb1ecd579e11e58fd3547" ns2:_="" ns3:_="">
     <xsd:import namespace="bc76fe4c-a155-4cd4-b3ce-e749a30fe160"/>
@@ -68152,26 +68137,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4277783-1FC0-4518-9AC7-78441643C7FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{771927D8-23AB-4166-821E-2FB8CF69E88F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bc76fe4c-a155-4cd4-b3ce-e749a30fe160"/>
-    <ds:schemaRef ds:uri="be3055c3-5ee9-432b-9d2b-e9bb13d3524a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Loretta xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Skiee xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
+    <Marcusshortlist xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
+    <Notes xmlns="bc76fe4c-a155-4cd4-b3ce-e749a30fe160" xsi:nil="true"/>
+    <TaxCatchAll xmlns="be3055c3-5ee9-432b-9d2b-e9bb13d3524a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED3412-BBCC-49D1-9BBB-563663F97477}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -68188,4 +68178,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4277783-1FC0-4518-9AC7-78441643C7FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{771927D8-23AB-4166-821E-2FB8CF69E88F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bc76fe4c-a155-4cd4-b3ce-e749a30fe160"/>
+    <ds:schemaRef ds:uri="be3055c3-5ee9-432b-9d2b-e9bb13d3524a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>